--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/08-report/CYC-1-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/08-report/CYC-1-cycle-report.xlsx
@@ -116,7 +116,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking baseline · Functional (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 132 test cases are designed, 74 of them automated in 58 Playwright scripts. Execution ran 74 automated cases for real: 71 passed and 3 failed (pass rate 95.9%). 3 defect(s) were raised from real failures: DEF-001 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-002 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-003 9 rooms in one search are rejected: returns 200 instead of 400.</t>
+    <t>Hotel booking baseline · Functional (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/Agentic-QE-MVP@demo/hotel-booking-platform (452df41) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 132 test cases are designed, 74 of them automated in 58 Playwright scripts. Execution ran 74 automated cases for real: 71 passed and 3 failed (pass rate 95.9%). 3 defect(s) were raised from real failures: DEF-001 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-002 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-003 9 rooms in one search are rejected: returns 200 instead of 400.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -149,7 +149,7 @@
     <t>jira-export</t>
   </si>
   <si>
-    <t>Jira export on GitHub (sri465inno/uc-agentic-quality-engineering@demo/jira-export): Jira REST API v3 JSON of AQPI-1, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
+    <t>Jira export on GitHub (sri465inno/Agentic-QE-MVP@demo/jira-export): Jira REST API v3 JSON of AQPI-1, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
   </si>
   <si>
     <t>Jira epic</t>
@@ -158,19 +158,19 @@
     <t>AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27</t>
   </si>
   <si>
-    <t>Jira export on GitHub (sri465inno/uc-agentic-quality-engineering@demo/jira-export): Jira REST API v3 JSON of AQPI-2, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
+    <t>Jira export on GitHub (sri465inno/Agentic-QE-MVP@demo/jira-export): Jira REST API v3 JSON of AQPI-2, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
   </si>
   <si>
     <t>Codebase</t>
   </si>
   <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41)</t>
+    <t>sri465inno/Agentic-QE-MVP@demo/hotel-booking-platform (452df41)</t>
   </si>
   <si>
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-05T16:26:38.592Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/Agentic-QE-MVP@demo/hotel-booking-platform (452df41) at 2026-10-05T16:43:26.346Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -4990,7 +4990,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-05T16:26:39.468Z</t>
+    <t>2026-10-05T16:43:27.155Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -23937,7 +23937,7 @@
         <v>1298</v>
       </c>
       <c r="E2" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -24055,7 +24055,7 @@
         <v>1298</v>
       </c>
       <c r="E8" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -24073,7 +24073,7 @@
         <v>1298</v>
       </c>
       <c r="E9" s="2">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -24091,7 +24091,7 @@
         <v>1298</v>
       </c>
       <c r="E10" s="2">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -24109,7 +24109,7 @@
         <v>1298</v>
       </c>
       <c r="E11" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -24127,7 +24127,7 @@
         <v>1298</v>
       </c>
       <c r="E12" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -24145,7 +24145,7 @@
         <v>1298</v>
       </c>
       <c r="E13" s="2">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -24223,7 +24223,7 @@
         <v>1298</v>
       </c>
       <c r="E17" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -24241,7 +24241,7 @@
         <v>1298</v>
       </c>
       <c r="E18" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -24299,7 +24299,7 @@
         <v>1298</v>
       </c>
       <c r="E21" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -24337,7 +24337,7 @@
         <v>1298</v>
       </c>
       <c r="E23" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -24355,7 +24355,7 @@
         <v>1298</v>
       </c>
       <c r="E24" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -24373,7 +24373,7 @@
         <v>1298</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -24391,7 +24391,7 @@
         <v>1298</v>
       </c>
       <c r="E26" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -24409,7 +24409,7 @@
         <v>1298</v>
       </c>
       <c r="E27" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -24445,7 +24445,7 @@
         <v>1298</v>
       </c>
       <c r="E29" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -24481,7 +24481,7 @@
         <v>1298</v>
       </c>
       <c r="E31" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -24537,7 +24537,7 @@
         <v>1298</v>
       </c>
       <c r="E34" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -24595,7 +24595,7 @@
         <v>1298</v>
       </c>
       <c r="E37" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -24633,7 +24633,7 @@
         <v>1298</v>
       </c>
       <c r="E39" s="2">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -24651,7 +24651,7 @@
         <v>1298</v>
       </c>
       <c r="E40" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -24749,7 +24749,7 @@
         <v>1298</v>
       </c>
       <c r="E45" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -24767,7 +24767,7 @@
         <v>1298</v>
       </c>
       <c r="E46" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -24785,7 +24785,7 @@
         <v>1298</v>
       </c>
       <c r="E47" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -24823,7 +24823,7 @@
         <v>1298</v>
       </c>
       <c r="E49" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -24841,7 +24841,7 @@
         <v>1298</v>
       </c>
       <c r="E50" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -24859,7 +24859,7 @@
         <v>1298</v>
       </c>
       <c r="E51" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -24977,7 +24977,7 @@
         <v>1298</v>
       </c>
       <c r="E57" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -24995,7 +24995,7 @@
         <v>1298</v>
       </c>
       <c r="E58" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -25033,7 +25033,7 @@
         <v>1298</v>
       </c>
       <c r="E60" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -25131,7 +25131,7 @@
         <v>1298</v>
       </c>
       <c r="E65" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -25149,7 +25149,7 @@
         <v>1298</v>
       </c>
       <c r="E66" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -25167,7 +25167,7 @@
         <v>1298</v>
       </c>
       <c r="E67" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -25225,7 +25225,7 @@
         <v>1298</v>
       </c>
       <c r="E70" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -25261,7 +25261,7 @@
         <v>1298</v>
       </c>
       <c r="E72" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -25299,7 +25299,7 @@
         <v>1298</v>
       </c>
       <c r="E74" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -25317,7 +25317,7 @@
         <v>1298</v>
       </c>
       <c r="E75" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -25353,7 +25353,7 @@
         <v>1298</v>
       </c>
       <c r="E77" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -25411,7 +25411,7 @@
         <v>1298</v>
       </c>
       <c r="E80" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -25429,7 +25429,7 @@
         <v>1298</v>
       </c>
       <c r="E81" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -25447,7 +25447,7 @@
         <v>1298</v>
       </c>
       <c r="E82" s="2">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -25525,7 +25525,7 @@
         <v>1298</v>
       </c>
       <c r="E86" s="2">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -25543,7 +25543,7 @@
         <v>1298</v>
       </c>
       <c r="E87" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -25561,7 +25561,7 @@
         <v>1298</v>
       </c>
       <c r="E88" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -25579,7 +25579,7 @@
         <v>1298</v>
       </c>
       <c r="E89" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -25597,7 +25597,7 @@
         <v>1298</v>
       </c>
       <c r="E90" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -25635,7 +25635,7 @@
         <v>1298</v>
       </c>
       <c r="E92" s="2">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -25673,7 +25673,7 @@
         <v>1298</v>
       </c>
       <c r="E94" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -25751,7 +25751,7 @@
         <v>1298</v>
       </c>
       <c r="E98" s="2">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -25869,7 +25869,7 @@
         <v>1298</v>
       </c>
       <c r="E104" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -25907,7 +25907,7 @@
         <v>1298</v>
       </c>
       <c r="E106" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -26045,7 +26045,7 @@
         <v>1298</v>
       </c>
       <c r="E113" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -26141,7 +26141,7 @@
         <v>1298</v>
       </c>
       <c r="E118" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -26159,7 +26159,7 @@
         <v>1301</v>
       </c>
       <c r="E119" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -26177,7 +26177,7 @@
         <v>1298</v>
       </c>
       <c r="E120" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -26195,7 +26195,7 @@
         <v>1298</v>
       </c>
       <c r="E121" s="2">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -26213,7 +26213,7 @@
         <v>1301</v>
       </c>
       <c r="E122" s="2">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -26249,7 +26249,7 @@
         <v>1298</v>
       </c>
       <c r="E124" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -26267,7 +26267,7 @@
         <v>1298</v>
       </c>
       <c r="E125" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -26285,7 +26285,7 @@
         <v>1298</v>
       </c>
       <c r="E126" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -26321,7 +26321,7 @@
         <v>1298</v>
       </c>
       <c r="E128" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -26339,7 +26339,7 @@
         <v>1298</v>
       </c>
       <c r="E129" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -26357,7 +26357,7 @@
         <v>1298</v>
       </c>
       <c r="E130" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -26393,7 +26393,7 @@
         <v>1298</v>
       </c>
       <c r="E132" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F132" s="2"/>
     </row>
